--- a/MyProject/sample-data/minta-penzugyi-adatok.xlsx
+++ b/MyProject/sample-data/minta-penzugyi-adatok.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,7 +425,7 @@
         <v>Lekérdezés időpontja</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-09-23 21:51:39</v>
+        <v>2026-09-25 19:41:18</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>Lekérdezés vége</v>
       </c>
       <c r="B6" t="str">
-        <v>2026.09.22</v>
+        <v>2026.09.21</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Példa Notino</v>
+        <v>HELOPAY*KNORR-BREMSE 6</v>
       </c>
       <c r="D16" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -548,7 +548,7 @@
         <v>x</v>
       </c>
       <c r="J16">
-        <v>-3523</v>
+        <v>-1761</v>
       </c>
       <c r="K16" t="str">
         <v>HUF</v>
@@ -562,7 +562,7 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Példa Sumup</v>
+        <v>Revolut**2024*</v>
       </c>
       <c r="D17" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -577,13 +577,13 @@
         <v>16</v>
       </c>
       <c r="H17" t="str">
-        <v>2026.08.09 00:00:00</v>
+        <v>2026.08.08 00:00:00</v>
       </c>
       <c r="I17" t="str">
         <v>x</v>
       </c>
       <c r="J17">
-        <v>-2031</v>
+        <v>-5999</v>
       </c>
       <c r="K17" t="str">
         <v>HUF</v>
@@ -597,13 +597,13 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Revolut*Teszt Anna</v>
       </c>
       <c r="D18" t="str">
-        <v>MUNKABÉR ÁTUTALÁS</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E18" t="str">
-        <v>Minta Munkáltató Kft. jövedelem</v>
+        <v>Közös számla</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -612,13 +612,13 @@
         <v>17</v>
       </c>
       <c r="H18" t="str">
-        <v>2026.08.10 00:00:00</v>
+        <v>2026.08.08 00:00:00</v>
       </c>
       <c r="I18" t="str">
         <v>x</v>
       </c>
       <c r="J18">
-        <v>380000</v>
+        <v>-25168</v>
       </c>
       <c r="K18" t="str">
         <v>HUF</v>
@@ -632,7 +632,7 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Fikció Pékség</v>
+        <v>Szerelmes Level Pekmuh</v>
       </c>
       <c r="D19" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -647,13 +647,13 @@
         <v>18</v>
       </c>
       <c r="H19" t="str">
-        <v>2026.08.10 00:00:00</v>
+        <v>2026.08.09 00:00:00</v>
       </c>
       <c r="I19" t="str">
         <v>x</v>
       </c>
       <c r="J19">
-        <v>-6323</v>
+        <v>-6557</v>
       </c>
       <c r="K19" t="str">
         <v>HUF</v>
@@ -667,13 +667,13 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>Fikció Azonnali fizetés</v>
+        <v>Minta Munkáltató Kft.</v>
       </c>
       <c r="D20" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>MUNKABÉR ÁTUTALÁS</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>jövedelem</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="H20" t="str">
-        <v>2026.08.11 00:00:00</v>
+        <v>2026.08.10 00:00:00</v>
       </c>
       <c r="I20" t="str">
         <v>x</v>
       </c>
       <c r="J20">
-        <v>-25268</v>
+        <v>380000</v>
       </c>
       <c r="K20" t="str">
         <v>HUF</v>
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>Teszt Telekom</v>
+        <v>SPAR Food &amp; Fuel</v>
       </c>
       <c r="D21" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -717,13 +717,13 @@
         <v>20</v>
       </c>
       <c r="H21" t="str">
-        <v>2026.08.12 00:00:00</v>
+        <v>2026.08.10 00:00:00</v>
       </c>
       <c r="I21" t="str">
         <v>x</v>
       </c>
       <c r="J21">
-        <v>-20851</v>
+        <v>-6323</v>
       </c>
       <c r="K21" t="str">
         <v>HUF</v>
@@ -737,13 +737,13 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>Revolut*Teszt Anna</v>
       </c>
       <c r="D22" t="str">
-        <v>KÉSZPÉNZFELVÉT ATM-BŐL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E22" t="str">
-        <v>Budapest, Teszt utca 1</v>
+        <v/>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -752,13 +752,13 @@
         <v>21</v>
       </c>
       <c r="H22" t="str">
-        <v>2026.08.13 00:00:00</v>
+        <v>2026.08.10 00:00:00</v>
       </c>
       <c r="I22" t="str">
         <v>x</v>
       </c>
       <c r="J22">
-        <v>-39054</v>
+        <v>29859</v>
       </c>
       <c r="K22" t="str">
         <v>HUF</v>
@@ -772,10 +772,10 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Teszt Szerelmes lev</v>
+        <v>PERSELY SZÁMLA</v>
       </c>
       <c r="D23" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -787,13 +787,13 @@
         <v>22</v>
       </c>
       <c r="H23" t="str">
-        <v>2026.08.14 00:00:00</v>
+        <v>2026.08.11 00:00:00</v>
       </c>
       <c r="I23" t="str">
         <v>x</v>
       </c>
       <c r="J23">
-        <v>-7763</v>
+        <v>-12661</v>
       </c>
       <c r="K23" t="str">
         <v>HUF</v>
@@ -807,7 +807,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Revolut**2024*</v>
+        <v>SIMPLEP*one</v>
       </c>
       <c r="D24" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -822,13 +822,13 @@
         <v>23</v>
       </c>
       <c r="H24" t="str">
-        <v>2026.08.15 00:00:00</v>
+        <v>2026.08.12 00:00:00</v>
       </c>
       <c r="I24" t="str">
         <v>x</v>
       </c>
       <c r="J24">
-        <v>-13278</v>
+        <v>-2434</v>
       </c>
       <c r="K24" t="str">
         <v>HUF</v>
@@ -842,7 +842,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Teszt Sörművház</v>
+        <v>arán bakery</v>
       </c>
       <c r="D25" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -857,13 +857,13 @@
         <v>24</v>
       </c>
       <c r="H25" t="str">
-        <v>2026.08.16 00:00:00</v>
+        <v>2026.08.12 00:00:00</v>
       </c>
       <c r="I25" t="str">
         <v>x</v>
       </c>
       <c r="J25">
-        <v>-1292</v>
+        <v>-7525</v>
       </c>
       <c r="K25" t="str">
         <v>HUF</v>
@@ -877,10 +877,10 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Fikció Benu</v>
+        <v>Revolut*Teszt Anna</v>
       </c>
       <c r="D26" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="H26" t="str">
-        <v>2026.08.18 00:00:00</v>
+        <v>2026.08.12 00:00:00</v>
       </c>
       <c r="I26" t="str">
         <v>x</v>
       </c>
       <c r="J26">
-        <v>-7783</v>
+        <v>28221</v>
       </c>
       <c r="K26" t="str">
         <v>HUF</v>
@@ -912,10 +912,10 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Minta Fodrász</v>
+        <v>Kata Példa</v>
       </c>
       <c r="D27" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -927,13 +927,13 @@
         <v>26</v>
       </c>
       <c r="H27" t="str">
-        <v>2026.08.20 00:00:00</v>
+        <v>2026.08.12 00:00:00</v>
       </c>
       <c r="I27" t="str">
         <v>x</v>
       </c>
       <c r="J27">
-        <v>-10285</v>
+        <v>23590</v>
       </c>
       <c r="K27" t="str">
         <v>HUF</v>
@@ -947,7 +947,7 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Minta Utalás</v>
+        <v>PRÍMA PÉK</v>
       </c>
       <c r="D28" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -962,13 +962,13 @@
         <v>27</v>
       </c>
       <c r="H28" t="str">
-        <v>2026.08.22 00:00:00</v>
+        <v>2026.08.13 00:00:00</v>
       </c>
       <c r="I28" t="str">
         <v>x</v>
       </c>
       <c r="J28">
-        <v>-11582</v>
+        <v>-7450</v>
       </c>
       <c r="K28" t="str">
         <v>HUF</v>
@@ -982,7 +982,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Minta Gyn</v>
+        <v>Revolut**2024*</v>
       </c>
       <c r="D29" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -997,13 +997,13 @@
         <v>28</v>
       </c>
       <c r="H29" t="str">
-        <v>2026.08.23 00:00:00</v>
+        <v>2026.08.13 00:00:00</v>
       </c>
       <c r="I29" t="str">
         <v>x</v>
       </c>
       <c r="J29">
-        <v>-16544</v>
+        <v>-13278</v>
       </c>
       <c r="K29" t="str">
         <v>HUF</v>
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Fikció Azonnali fizetés</v>
+        <v>APPLE.COM/BILL</v>
       </c>
       <c r="D30" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1032,13 +1032,13 @@
         <v>29</v>
       </c>
       <c r="H30" t="str">
-        <v>2026.08.24 00:00:00</v>
+        <v>2026.08.14 00:00:00</v>
       </c>
       <c r="I30" t="str">
         <v>x</v>
       </c>
       <c r="J30">
-        <v>-16618</v>
+        <v>-1490</v>
       </c>
       <c r="K30" t="str">
         <v>HUF</v>
@@ -1052,7 +1052,7 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Minta Lidl</v>
+        <v>My Green Cup</v>
       </c>
       <c r="D31" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1067,13 +1067,13 @@
         <v>30</v>
       </c>
       <c r="H31" t="str">
-        <v>2026.08.27 00:00:00</v>
+        <v>2026.08.14 00:00:00</v>
       </c>
       <c r="I31" t="str">
         <v>x</v>
       </c>
       <c r="J31">
-        <v>-6776</v>
+        <v>-4199</v>
       </c>
       <c r="K31" t="str">
         <v>HUF</v>
@@ -1087,13 +1087,13 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Teszt Átutalás</v>
+        <v>Minta Péter</v>
       </c>
       <c r="D32" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>Havi Lakbér</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="H32" t="str">
-        <v>2026.08.28 00:00:00</v>
+        <v>2026.08.15 00:00:00</v>
       </c>
       <c r="I32" t="str">
         <v>x</v>
       </c>
       <c r="J32">
-        <v>-16145</v>
+        <v>-110000</v>
       </c>
       <c r="K32" t="str">
         <v>HUF</v>
@@ -1122,7 +1122,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Revolut**2024*</v>
+        <v>Muller Drogeria 5257</v>
       </c>
       <c r="D33" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1137,13 +1137,13 @@
         <v>32</v>
       </c>
       <c r="H33" t="str">
-        <v>2026.08.28 00:00:00</v>
+        <v>2026.08.15 00:00:00</v>
       </c>
       <c r="I33" t="str">
         <v>x</v>
       </c>
       <c r="J33">
-        <v>-7309</v>
+        <v>-7138</v>
       </c>
       <c r="K33" t="str">
         <v>HUF</v>
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Fikció Wokbar</v>
+        <v>LIDL HU 101 Balatonlel</v>
       </c>
       <c r="D34" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1172,13 +1172,13 @@
         <v>33</v>
       </c>
       <c r="H34" t="str">
-        <v>2026.08.29 00:00:00</v>
+        <v>2026.08.16 00:00:00</v>
       </c>
       <c r="I34" t="str">
         <v>x</v>
       </c>
       <c r="J34">
-        <v>-3759</v>
+        <v>-4415</v>
       </c>
       <c r="K34" t="str">
         <v>HUF</v>
@@ -1192,7 +1192,7 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Minta Pizzé</v>
+        <v>foodora</v>
       </c>
       <c r="D35" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1207,13 +1207,13 @@
         <v>34</v>
       </c>
       <c r="H35" t="str">
-        <v>2026.08.30 00:00:00</v>
+        <v>2026.08.17 00:00:00</v>
       </c>
       <c r="I35" t="str">
         <v>x</v>
       </c>
       <c r="J35">
-        <v>-5435</v>
+        <v>-4791</v>
       </c>
       <c r="K35" t="str">
         <v>HUF</v>
@@ -1227,10 +1227,10 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Minta Fodrász</v>
+        <v>PIREX PAPÍR ETELE</v>
       </c>
       <c r="D36" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>VISSZATÉRÍTÉS</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1242,13 +1242,13 @@
         <v>35</v>
       </c>
       <c r="H36" t="str">
-        <v>2026.08.31 00:00:00</v>
+        <v>2026.08.17 00:00:00</v>
       </c>
       <c r="I36" t="str">
         <v>x</v>
       </c>
       <c r="J36">
-        <v>-11721</v>
+        <v>17888</v>
       </c>
       <c r="K36" t="str">
         <v>HUF</v>
@@ -1262,10 +1262,10 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Példa Bakery</v>
+        <v>Revolut*Teszt Anna</v>
       </c>
       <c r="D37" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1277,13 +1277,13 @@
         <v>36</v>
       </c>
       <c r="H37" t="str">
-        <v>2026.09.01 00:00:00</v>
+        <v>2026.08.17 00:00:00</v>
       </c>
       <c r="I37" t="str">
         <v>x</v>
       </c>
       <c r="J37">
-        <v>-7248</v>
+        <v>21790</v>
       </c>
       <c r="K37" t="str">
         <v>HUF</v>
@@ -1297,13 +1297,13 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Fikció Hobby</v>
+        <v>Revolut*Teszt Anna</v>
       </c>
       <c r="D38" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>Közös számla</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -1312,13 +1312,13 @@
         <v>37</v>
       </c>
       <c r="H38" t="str">
-        <v>2026.09.02 00:00:00</v>
+        <v>2026.08.17 00:00:00</v>
       </c>
       <c r="I38" t="str">
         <v>x</v>
       </c>
       <c r="J38">
-        <v>-2704</v>
+        <v>-23427</v>
       </c>
       <c r="K38" t="str">
         <v>HUF</v>
@@ -1332,7 +1332,7 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Fikció Fitness</v>
+        <v>Budapest Park</v>
       </c>
       <c r="D39" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1347,13 +1347,13 @@
         <v>38</v>
       </c>
       <c r="H39" t="str">
-        <v>2026.09.03 00:00:00</v>
+        <v>2026.08.18 00:00:00</v>
       </c>
       <c r="I39" t="str">
         <v>x</v>
       </c>
       <c r="J39">
-        <v>-5705</v>
+        <v>-3758</v>
       </c>
       <c r="K39" t="str">
         <v>HUF</v>
@@ -1367,10 +1367,10 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Fikció Pékség</v>
+        <v>PERSELY SZÁMLA</v>
       </c>
       <c r="D40" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1382,13 +1382,13 @@
         <v>39</v>
       </c>
       <c r="H40" t="str">
-        <v>2026.09.04 00:00:00</v>
+        <v>2026.08.19 00:00:00</v>
       </c>
       <c r="I40" t="str">
         <v>x</v>
       </c>
       <c r="J40">
-        <v>-6410</v>
+        <v>14897</v>
       </c>
       <c r="K40" t="str">
         <v>HUF</v>
@@ -1402,7 +1402,7 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Fikció Aldi</v>
+        <v>DECATHLON-CORVIN</v>
       </c>
       <c r="D41" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1417,13 +1417,13 @@
         <v>40</v>
       </c>
       <c r="H41" t="str">
-        <v>2026.09.06 00:00:00</v>
+        <v>2026.08.19 00:00:00</v>
       </c>
       <c r="I41" t="str">
         <v>x</v>
       </c>
       <c r="J41">
-        <v>-2108</v>
+        <v>-18669</v>
       </c>
       <c r="K41" t="str">
         <v>HUF</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Revolut**2024*</v>
+        <v>Pesti Pilates</v>
       </c>
       <c r="D42" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1452,13 +1452,13 @@
         <v>41</v>
       </c>
       <c r="H42" t="str">
-        <v>2026.09.06 00:00:00</v>
+        <v>2026.08.21 00:00:00</v>
       </c>
       <c r="I42" t="str">
         <v>x</v>
       </c>
       <c r="J42">
-        <v>-7559</v>
+        <v>-9679</v>
       </c>
       <c r="K42" t="str">
         <v>HUF</v>
@@ -1472,13 +1472,13 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Teszt Cocacola</v>
+        <v/>
       </c>
       <c r="D43" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>KÉSZPÉNZFELVÉT ATM-BŐL</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>Budapest, Teszt utca 1</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -1487,13 +1487,13 @@
         <v>42</v>
       </c>
       <c r="H43" t="str">
-        <v>2026.09.09 00:00:00</v>
+        <v>2026.08.21 00:00:00</v>
       </c>
       <c r="I43" t="str">
         <v>x</v>
       </c>
       <c r="J43">
-        <v>-2963</v>
+        <v>-25016</v>
       </c>
       <c r="K43" t="str">
         <v>HUF</v>
@@ -1507,10 +1507,10 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Revolut**2024*</v>
+        <v>Példa Kata</v>
       </c>
       <c r="D44" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>AZONNALI FIZETÉS</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1522,13 +1522,13 @@
         <v>43</v>
       </c>
       <c r="H44" t="str">
-        <v>2026.09.09 00:00:00</v>
+        <v>2026.08.21 00:00:00</v>
       </c>
       <c r="I44" t="str">
         <v>x</v>
       </c>
       <c r="J44">
-        <v>-11146</v>
+        <v>-17675</v>
       </c>
       <c r="K44" t="str">
         <v>HUF</v>
@@ -1542,13 +1542,13 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>SIMPLEP*TELEKOM2597</v>
       </c>
       <c r="D45" t="str">
-        <v>MUNKABÉR ÁTUTALÁS</v>
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
       </c>
       <c r="E45" t="str">
-        <v>Minta Munkáltató Kft. jövedelem</v>
+        <v/>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -1557,13 +1557,13 @@
         <v>44</v>
       </c>
       <c r="H45" t="str">
-        <v>2026.09.10 00:00:00</v>
+        <v>2026.08.22 00:00:00</v>
       </c>
       <c r="I45" t="str">
         <v>x</v>
       </c>
       <c r="J45">
-        <v>380000</v>
+        <v>-5479</v>
       </c>
       <c r="K45" t="str">
         <v>HUF</v>
@@ -1577,7 +1577,7 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Fikció Műköröm</v>
+        <v>Lidl</v>
       </c>
       <c r="D46" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1592,13 +1592,13 @@
         <v>45</v>
       </c>
       <c r="H46" t="str">
-        <v>2026.09.11 00:00:00</v>
+        <v>2026.08.22 00:00:00</v>
       </c>
       <c r="I46" t="str">
         <v>x</v>
       </c>
       <c r="J46">
-        <v>-19148</v>
+        <v>-3993</v>
       </c>
       <c r="K46" t="str">
         <v>HUF</v>
@@ -1612,13 +1612,13 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Minta Fodrász</v>
+        <v>Példa Fanni</v>
       </c>
       <c r="D47" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>Fodrász</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -1627,13 +1627,13 @@
         <v>46</v>
       </c>
       <c r="H47" t="str">
-        <v>2026.09.12 00:00:00</v>
+        <v>2026.08.23 00:00:00</v>
       </c>
       <c r="I47" t="str">
         <v>x</v>
       </c>
       <c r="J47">
-        <v>-6362</v>
+        <v>-9062</v>
       </c>
       <c r="K47" t="str">
         <v>HUF</v>
@@ -1647,7 +1647,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Teszt Telekom</v>
+        <v>HELOPAY*KNORR-BREMSE 6</v>
       </c>
       <c r="D48" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1662,13 +1662,13 @@
         <v>47</v>
       </c>
       <c r="H48" t="str">
-        <v>2026.09.14 00:00:00</v>
+        <v>2026.08.23 00:00:00</v>
       </c>
       <c r="I48" t="str">
         <v>x</v>
       </c>
       <c r="J48">
-        <v>-23036</v>
+        <v>-4903</v>
       </c>
       <c r="K48" t="str">
         <v>HUF</v>
@@ -1682,13 +1682,13 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Fikció Jegy.hu</v>
+        <v/>
       </c>
       <c r="D49" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>KÉSZPÉNZFELVÉT ATM-BŐL</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>Budapest, Teszt utca 1</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -1697,13 +1697,13 @@
         <v>48</v>
       </c>
       <c r="H49" t="str">
-        <v>2026.09.15 00:00:00</v>
+        <v>2026.08.23 00:00:00</v>
       </c>
       <c r="I49" t="str">
         <v>x</v>
       </c>
       <c r="J49">
-        <v>-14356</v>
+        <v>-28745</v>
       </c>
       <c r="K49" t="str">
         <v>HUF</v>
@@ -1717,7 +1717,7 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Fikció Jegy.hu</v>
+        <v>Szerelmes Levél</v>
       </c>
       <c r="D50" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1732,13 +1732,13 @@
         <v>49</v>
       </c>
       <c r="H50" t="str">
-        <v>2026.09.16 00:00:00</v>
+        <v>2026.08.24 00:00:00</v>
       </c>
       <c r="I50" t="str">
         <v>x</v>
       </c>
       <c r="J50">
-        <v>-13797</v>
+        <v>-5934</v>
       </c>
       <c r="K50" t="str">
         <v>HUF</v>
@@ -1752,10 +1752,10 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Teszt Gyn obs</v>
+        <v/>
       </c>
       <c r="D51" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ESETI MEGBÍZÁSOK KÖLTSÉGE</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1767,13 +1767,13 @@
         <v>50</v>
       </c>
       <c r="H51" t="str">
-        <v>2026.09.17 00:00:00</v>
+        <v>2026.08.25 00:00:00</v>
       </c>
       <c r="I51" t="str">
         <v>x</v>
       </c>
       <c r="J51">
-        <v>-7746</v>
+        <v>-155</v>
       </c>
       <c r="K51" t="str">
         <v>HUF</v>
@@ -1787,10 +1787,10 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Minta Vision express</v>
+        <v>Revolut*Teszt Anna</v>
       </c>
       <c r="D52" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>ÁTUTALÁS</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1802,13 +1802,13 @@
         <v>51</v>
       </c>
       <c r="H52" t="str">
-        <v>2026.09.18 00:00:00</v>
+        <v>2026.08.25 00:00:00</v>
       </c>
       <c r="I52" t="str">
         <v>x</v>
       </c>
       <c r="J52">
-        <v>-10335</v>
+        <v>29280</v>
       </c>
       <c r="K52" t="str">
         <v>HUF</v>
@@ -1822,7 +1822,7 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Minta Utalás</v>
+        <v>SMPLPAY*KNORR-BREMSE 6</v>
       </c>
       <c r="D53" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1837,13 +1837,13 @@
         <v>52</v>
       </c>
       <c r="H53" t="str">
-        <v>2026.09.19 00:00:00</v>
+        <v>2026.08.25 00:00:00</v>
       </c>
       <c r="I53" t="str">
         <v>x</v>
       </c>
       <c r="J53">
-        <v>-9832</v>
+        <v>-1088</v>
       </c>
       <c r="K53" t="str">
         <v>HUF</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Fikció Kávé</v>
+        <v>BARION *Jegy.hu</v>
       </c>
       <c r="D54" t="str">
         <v>VÁSÁRLÁS KÁRTYÁVAL</v>
@@ -1872,13 +1872,13 @@
         <v>53</v>
       </c>
       <c r="H54" t="str">
-        <v>2026.09.20 00:00:00</v>
+        <v>2026.08.26 00:00:00</v>
       </c>
       <c r="I54" t="str">
         <v>x</v>
       </c>
       <c r="J54">
-        <v>-5974</v>
+        <v>-6013</v>
       </c>
       <c r="K54" t="str">
         <v>HUF</v>
@@ -1892,13 +1892,13 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Teszt Rossmann</v>
+        <v/>
       </c>
       <c r="D55" t="str">
-        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+        <v>KÉSZPÉNZFELVÉT ATM-BŐL</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>Budapest, Teszt utca 1</v>
       </c>
       <c r="F55" t="str">
         <v/>
@@ -1907,28 +1907,1428 @@
         <v>54</v>
       </c>
       <c r="H55" t="str">
+        <v>2026.08.26 00:00:00</v>
+      </c>
+      <c r="I55" t="str">
+        <v>x</v>
+      </c>
+      <c r="J55">
+        <v>-22006</v>
+      </c>
+      <c r="K55" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v>Revolut*Teszt Anna</v>
+      </c>
+      <c r="D56" t="str">
+        <v>ÁTUTALÁS</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Közös számla</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>55</v>
+      </c>
+      <c r="H56" t="str">
+        <v>2026.08.26 00:00:00</v>
+      </c>
+      <c r="I56" t="str">
+        <v>x</v>
+      </c>
+      <c r="J56">
+        <v>-17339</v>
+      </c>
+      <c r="K56" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v>COOP MINI ÉLELMISZER</v>
+      </c>
+      <c r="D57" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>56</v>
+      </c>
+      <c r="H57" t="str">
+        <v>2026.08.27 00:00:00</v>
+      </c>
+      <c r="I57" t="str">
+        <v>x</v>
+      </c>
+      <c r="J57">
+        <v>-1924</v>
+      </c>
+      <c r="K57" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v>Revolut**2024*</v>
+      </c>
+      <c r="D58" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>57</v>
+      </c>
+      <c r="H58" t="str">
+        <v>2026.08.27 00:00:00</v>
+      </c>
+      <c r="I58" t="str">
+        <v>x</v>
+      </c>
+      <c r="J58">
+        <v>-11955</v>
+      </c>
+      <c r="K58" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v>HELOPAY*KNORR-BREMSE 6</v>
+      </c>
+      <c r="D59" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>58</v>
+      </c>
+      <c r="H59" t="str">
+        <v>2026.08.28 00:00:00</v>
+      </c>
+      <c r="I59" t="str">
+        <v>x</v>
+      </c>
+      <c r="J59">
+        <v>-2890</v>
+      </c>
+      <c r="K59" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v/>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v>Bolt</v>
+      </c>
+      <c r="D60" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>59</v>
+      </c>
+      <c r="H60" t="str">
+        <v>2026.08.29 00:00:00</v>
+      </c>
+      <c r="I60" t="str">
+        <v>x</v>
+      </c>
+      <c r="J60">
+        <v>-11122</v>
+      </c>
+      <c r="K60" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v/>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v>BKK AUTOMATA - I11</v>
+      </c>
+      <c r="D61" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>60</v>
+      </c>
+      <c r="H61" t="str">
+        <v>2026.08.30 00:00:00</v>
+      </c>
+      <c r="I61" t="str">
+        <v>x</v>
+      </c>
+      <c r="J61">
+        <v>-4502</v>
+      </c>
+      <c r="K61" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v/>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v>HELOPAY*KNORR-BREMSE 6</v>
+      </c>
+      <c r="D62" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>61</v>
+      </c>
+      <c r="H62" t="str">
+        <v>2026.09.01 00:00:00</v>
+      </c>
+      <c r="I62" t="str">
+        <v>x</v>
+      </c>
+      <c r="J62">
+        <v>-3395</v>
+      </c>
+      <c r="K62" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v>SPAR MAGYARORSZÁG KFT</v>
+      </c>
+      <c r="D63" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>62</v>
+      </c>
+      <c r="H63" t="str">
+        <v>2026.09.02 00:00:00</v>
+      </c>
+      <c r="I63" t="str">
+        <v>x</v>
+      </c>
+      <c r="J63">
+        <v>-5748</v>
+      </c>
+      <c r="K63" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v/>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v>B CINEMA CITY ALLEE</v>
+      </c>
+      <c r="D64" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>63</v>
+      </c>
+      <c r="H64" t="str">
+        <v>2026.09.03 00:00:00</v>
+      </c>
+      <c r="I64" t="str">
+        <v>x</v>
+      </c>
+      <c r="J64">
+        <v>-6854</v>
+      </c>
+      <c r="K64" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v>LIDL HU 274 Budapest</v>
+      </c>
+      <c r="D65" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>64</v>
+      </c>
+      <c r="H65" t="str">
+        <v>2026.09.04 00:00:00</v>
+      </c>
+      <c r="I65" t="str">
+        <v>x</v>
+      </c>
+      <c r="J65">
+        <v>-7698</v>
+      </c>
+      <c r="K65" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v>Revolut*Teszt Anna</v>
+      </c>
+      <c r="D66" t="str">
+        <v>ÁTUTALÁS</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Közös számla</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>65</v>
+      </c>
+      <c r="H66" t="str">
+        <v>2026.09.04 00:00:00</v>
+      </c>
+      <c r="I66" t="str">
+        <v>x</v>
+      </c>
+      <c r="J66">
+        <v>-18443</v>
+      </c>
+      <c r="K66" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v>KEG Sörművház</v>
+      </c>
+      <c r="D67" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>66</v>
+      </c>
+      <c r="H67" t="str">
+        <v>2026.09.05 00:00:00</v>
+      </c>
+      <c r="I67" t="str">
+        <v>x</v>
+      </c>
+      <c r="J67">
+        <v>-5759</v>
+      </c>
+      <c r="K67" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v/>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v>LIPÓTI PÉKSÉG</v>
+      </c>
+      <c r="D68" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v>67</v>
+      </c>
+      <c r="H68" t="str">
+        <v>2026.09.06 00:00:00</v>
+      </c>
+      <c r="I68" t="str">
+        <v>x</v>
+      </c>
+      <c r="J68">
+        <v>-3386</v>
+      </c>
+      <c r="K68" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v/>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v>Pesti Pilates</v>
+      </c>
+      <c r="D69" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>68</v>
+      </c>
+      <c r="H69" t="str">
+        <v>2026.09.07 00:00:00</v>
+      </c>
+      <c r="I69" t="str">
+        <v>x</v>
+      </c>
+      <c r="J69">
+        <v>-13049</v>
+      </c>
+      <c r="K69" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v>DM 233.SZ.</v>
+      </c>
+      <c r="D70" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>69</v>
+      </c>
+      <c r="H70" t="str">
+        <v>2026.09.08 00:00:00</v>
+      </c>
+      <c r="I70" t="str">
+        <v>x</v>
+      </c>
+      <c r="J70">
+        <v>-3383</v>
+      </c>
+      <c r="K70" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v/>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v>Gyn Obs</v>
+      </c>
+      <c r="D71" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v>70</v>
+      </c>
+      <c r="H71" t="str">
+        <v>2026.09.09 00:00:00</v>
+      </c>
+      <c r="I71" t="str">
+        <v>x</v>
+      </c>
+      <c r="J71">
+        <v>-15760</v>
+      </c>
+      <c r="K71" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v/>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v>Revolut**2024*</v>
+      </c>
+      <c r="D72" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>71</v>
+      </c>
+      <c r="H72" t="str">
+        <v>2026.09.09 00:00:00</v>
+      </c>
+      <c r="I72" t="str">
+        <v>x</v>
+      </c>
+      <c r="J72">
+        <v>-5494</v>
+      </c>
+      <c r="K72" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v/>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v>Minta Munkáltató Kft.</v>
+      </c>
+      <c r="D73" t="str">
+        <v>MUNKABÉR ÁTUTALÁS</v>
+      </c>
+      <c r="E73" t="str">
+        <v>jövedelem</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>72</v>
+      </c>
+      <c r="H73" t="str">
+        <v>2026.09.10 00:00:00</v>
+      </c>
+      <c r="I73" t="str">
+        <v>x</v>
+      </c>
+      <c r="J73">
+        <v>380000</v>
+      </c>
+      <c r="K73" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v/>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v>DM 233.SZ.</v>
+      </c>
+      <c r="D74" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>73</v>
+      </c>
+      <c r="H74" t="str">
+        <v>2026.09.10 00:00:00</v>
+      </c>
+      <c r="I74" t="str">
+        <v>x</v>
+      </c>
+      <c r="J74">
+        <v>-9149</v>
+      </c>
+      <c r="K74" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v/>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>KÉSZPÉNZFELVÉT ATM-BŐL</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Budapest, Teszt utca 1</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>74</v>
+      </c>
+      <c r="H75" t="str">
+        <v>2026.09.10 00:00:00</v>
+      </c>
+      <c r="I75" t="str">
+        <v>x</v>
+      </c>
+      <c r="J75">
+        <v>-14541</v>
+      </c>
+      <c r="K75" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v/>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v>PERSELY SZÁMLA</v>
+      </c>
+      <c r="D76" t="str">
+        <v>ÁTUTALÁS</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>75</v>
+      </c>
+      <c r="H76" t="str">
+        <v>2026.09.11 00:00:00</v>
+      </c>
+      <c r="I76" t="str">
+        <v>x</v>
+      </c>
+      <c r="J76">
+        <v>-14017</v>
+      </c>
+      <c r="K76" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v/>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v>SPAR MAGYARORSZAG KFT.</v>
+      </c>
+      <c r="D77" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>76</v>
+      </c>
+      <c r="H77" t="str">
+        <v>2026.09.11 00:00:00</v>
+      </c>
+      <c r="I77" t="str">
+        <v>x</v>
+      </c>
+      <c r="J77">
+        <v>-7863</v>
+      </c>
+      <c r="K77" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v/>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v>Tchibo 7855</v>
+      </c>
+      <c r="D78" t="str">
+        <v>VISSZATÉRÍTÉS</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>77</v>
+      </c>
+      <c r="H78" t="str">
+        <v>2026.09.11 00:00:00</v>
+      </c>
+      <c r="I78" t="str">
+        <v>x</v>
+      </c>
+      <c r="J78">
+        <v>12534</v>
+      </c>
+      <c r="K78" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v/>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v>SIMPLEP*one</v>
+      </c>
+      <c r="D79" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v>78</v>
+      </c>
+      <c r="H79" t="str">
+        <v>2026.09.12 00:00:00</v>
+      </c>
+      <c r="I79" t="str">
+        <v>x</v>
+      </c>
+      <c r="J79">
+        <v>-2843</v>
+      </c>
+      <c r="K79" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v/>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v>Revolut**2024*</v>
+      </c>
+      <c r="D80" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>79</v>
+      </c>
+      <c r="H80" t="str">
+        <v>2026.09.12 00:00:00</v>
+      </c>
+      <c r="I80" t="str">
+        <v>x</v>
+      </c>
+      <c r="J80">
+        <v>-7039</v>
+      </c>
+      <c r="K80" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v>Lidl</v>
+      </c>
+      <c r="D81" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v>80</v>
+      </c>
+      <c r="H81" t="str">
+        <v>2026.09.13 00:00:00</v>
+      </c>
+      <c r="I81" t="str">
+        <v>x</v>
+      </c>
+      <c r="J81">
+        <v>-5433</v>
+      </c>
+      <c r="K81" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v/>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v>KÉSZPÉNZFELVÉT ATM-BŐL</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Budapest, Teszt utca 1</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>81</v>
+      </c>
+      <c r="H82" t="str">
+        <v>2026.09.13 00:00:00</v>
+      </c>
+      <c r="I82" t="str">
+        <v>x</v>
+      </c>
+      <c r="J82">
+        <v>-30591</v>
+      </c>
+      <c r="K82" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v/>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v>Revolut*Teszt Anna</v>
+      </c>
+      <c r="D83" t="str">
+        <v>ÁTUTALÁS</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Közös számla</v>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>82</v>
+      </c>
+      <c r="H83" t="str">
+        <v>2026.09.13 00:00:00</v>
+      </c>
+      <c r="I83" t="str">
+        <v>x</v>
+      </c>
+      <c r="J83">
+        <v>-33657</v>
+      </c>
+      <c r="K83" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v/>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v>APPLE.COM/BILL</v>
+      </c>
+      <c r="D84" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>83</v>
+      </c>
+      <c r="H84" t="str">
+        <v>2026.09.14 00:00:00</v>
+      </c>
+      <c r="I84" t="str">
+        <v>x</v>
+      </c>
+      <c r="J84">
+        <v>-1490</v>
+      </c>
+      <c r="K84" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v/>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v>LIPÓTI PÉKSÉG</v>
+      </c>
+      <c r="D85" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>84</v>
+      </c>
+      <c r="H85" t="str">
+        <v>2026.09.14 00:00:00</v>
+      </c>
+      <c r="I85" t="str">
+        <v>x</v>
+      </c>
+      <c r="J85">
+        <v>-7514</v>
+      </c>
+      <c r="K85" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v/>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v>Minta Péter</v>
+      </c>
+      <c r="D86" t="str">
+        <v>ÁTUTALÁS</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Havi Lakbér</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v>85</v>
+      </c>
+      <c r="H86" t="str">
+        <v>2026.09.15 00:00:00</v>
+      </c>
+      <c r="I86" t="str">
+        <v>x</v>
+      </c>
+      <c r="J86">
+        <v>-110000</v>
+      </c>
+      <c r="K86" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v/>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v>LIDL HU 274 Budapest</v>
+      </c>
+      <c r="D87" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>86</v>
+      </c>
+      <c r="H87" t="str">
+        <v>2026.09.15 00:00:00</v>
+      </c>
+      <c r="I87" t="str">
+        <v>x</v>
+      </c>
+      <c r="J87">
+        <v>-1941</v>
+      </c>
+      <c r="K87" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v/>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v>RESERVED ALLEE 6912320</v>
+      </c>
+      <c r="D88" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v>87</v>
+      </c>
+      <c r="H88" t="str">
+        <v>2026.09.16 00:00:00</v>
+      </c>
+      <c r="I88" t="str">
+        <v>x</v>
+      </c>
+      <c r="J88">
+        <v>-22372</v>
+      </c>
+      <c r="K88" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v/>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v>DECATHLON-CORVIN</v>
+      </c>
+      <c r="D89" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>88</v>
+      </c>
+      <c r="H89" t="str">
+        <v>2026.09.17 00:00:00</v>
+      </c>
+      <c r="I89" t="str">
+        <v>x</v>
+      </c>
+      <c r="J89">
+        <v>-23416</v>
+      </c>
+      <c r="K89" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v/>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v>Revolut**2024*</v>
+      </c>
+      <c r="D90" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v>89</v>
+      </c>
+      <c r="H90" t="str">
+        <v>2026.09.17 00:00:00</v>
+      </c>
+      <c r="I90" t="str">
+        <v>x</v>
+      </c>
+      <c r="J90">
+        <v>-14305</v>
+      </c>
+      <c r="K90" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v/>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v>LIPÓTI PÉKSÉG</v>
+      </c>
+      <c r="D91" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v>90</v>
+      </c>
+      <c r="H91" t="str">
+        <v>2026.09.18 00:00:00</v>
+      </c>
+      <c r="I91" t="str">
+        <v>x</v>
+      </c>
+      <c r="J91">
+        <v>-4806</v>
+      </c>
+      <c r="K91" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v/>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v>SIMPLEP*BudapestGO app</v>
+      </c>
+      <c r="D92" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v>91</v>
+      </c>
+      <c r="H92" t="str">
+        <v>2026.09.19 00:00:00</v>
+      </c>
+      <c r="I92" t="str">
+        <v>x</v>
+      </c>
+      <c r="J92">
+        <v>-11271</v>
+      </c>
+      <c r="K92" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>LIDL HU 274 Budapest</v>
+      </c>
+      <c r="D93" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v>92</v>
+      </c>
+      <c r="H93" t="str">
+        <v>2026.09.20 00:00:00</v>
+      </c>
+      <c r="I93" t="str">
+        <v>x</v>
+      </c>
+      <c r="J93">
+        <v>-6349</v>
+      </c>
+      <c r="K93" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v/>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>Padthai Wokbar (Allee)</v>
+      </c>
+      <c r="D94" t="str">
+        <v>VÁSÁRLÁS KÁRTYÁVAL</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>93</v>
+      </c>
+      <c r="H94" t="str">
         <v>2026.09.21 00:00:00</v>
       </c>
-      <c r="I55" t="str">
-        <v>x</v>
-      </c>
-      <c r="J55">
-        <v>-10466</v>
-      </c>
-      <c r="K55" t="str">
+      <c r="I94" t="str">
+        <v>x</v>
+      </c>
+      <c r="J94">
+        <v>-3999</v>
+      </c>
+      <c r="K94" t="str">
+        <v>HUF</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v/>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>Fikció Zsolt</v>
+      </c>
+      <c r="D95" t="str">
+        <v>AZONNALI FIZETÉS</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>94</v>
+      </c>
+      <c r="H95" t="str">
+        <v>2026.09.21 00:00:00</v>
+      </c>
+      <c r="I95" t="str">
+        <v>x</v>
+      </c>
+      <c r="J95">
+        <v>-13606</v>
+      </c>
+      <c r="K95" t="str">
         <v>HUF</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K95"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1976,10 +3376,10 @@
         <v>2026.08.09 01:00</v>
       </c>
       <c r="E2" t="str">
-        <v>Teszt Simplep*one</v>
+        <v>Anthropic</v>
       </c>
       <c r="F2">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1991,7 +3391,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J2">
-        <v>149985</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3">
@@ -2002,16 +3402,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C3" t="str">
-        <v>2026.08.14 00:00</v>
+        <v>2026.08.12 00:00</v>
       </c>
       <c r="D3" t="str">
-        <v>2026.08.14 01:00</v>
+        <v>2026.08.12 01:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Teszt Átutalás</v>
+        <v>Cafe+Co HU 223562</v>
       </c>
       <c r="F3">
-        <v>-5</v>
+        <v>-36</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2023,27 +3423,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J3">
-        <v>149980</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Csere</v>
       </c>
       <c r="B4" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C4" t="str">
-        <v>2026.08.15 00:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="D4" t="str">
-        <v>2026.08.15 01:00</v>
+        <v>2026.08.13 01:00</v>
       </c>
       <c r="E4" t="str">
-        <v>Teszt Ecofamily</v>
+        <v>Devizaváltás EUR pénznemre</v>
       </c>
       <c r="F4">
-        <v>-26</v>
+        <v>150</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2055,7 +3455,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J4">
-        <v>149954</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5">
@@ -2066,16 +3466,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C5" t="str">
-        <v>2026.08.17 00:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="D5" t="str">
-        <v>2026.08.17 01:00</v>
+        <v>2026.08.13 01:00</v>
       </c>
       <c r="E5" t="str">
-        <v>Minta Orvos</v>
+        <v>Bolt</v>
       </c>
       <c r="F5">
-        <v>-39</v>
+        <v>-13</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2087,7 +3487,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J5">
-        <v>149915</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6">
@@ -2098,16 +3498,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C6" t="str">
-        <v>2026.08.20 00:00</v>
+        <v>2026.08.16 00:00</v>
       </c>
       <c r="D6" t="str">
-        <v>2026.08.20 01:00</v>
+        <v>2026.08.16 01:00</v>
       </c>
       <c r="E6" t="str">
-        <v>Példa Notino</v>
+        <v>BKK AUTOMATA - G99</v>
       </c>
       <c r="F6">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2119,7 +3519,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J6">
-        <v>149906</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7">
@@ -2130,16 +3530,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C7" t="str">
-        <v>2026.08.22 00:00</v>
+        <v>2026.08.21 00:00</v>
       </c>
       <c r="D7" t="str">
-        <v>2026.08.22 01:00</v>
+        <v>2026.08.21 01:00</v>
       </c>
       <c r="E7" t="str">
-        <v>Minta Lidl</v>
+        <v>DECATHLON-CORVIN</v>
       </c>
       <c r="F7">
-        <v>-20</v>
+        <v>-38</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2151,7 +3551,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J7">
-        <v>149886</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -2162,16 +3562,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C8" t="str">
-        <v>2026.08.25 00:00</v>
+        <v>2026.08.22 00:00</v>
       </c>
       <c r="D8" t="str">
-        <v>2026.08.25 01:00</v>
+        <v>2026.08.22 01:00</v>
       </c>
       <c r="E8" t="str">
-        <v>Minta Utalás</v>
+        <v>SIMPLEP*BudapestGO app</v>
       </c>
       <c r="F8">
-        <v>-38</v>
+        <v>-34</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2183,7 +3583,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J8">
-        <v>149848</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9">
@@ -2194,16 +3594,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C9" t="str">
-        <v>2026.08.26 00:00</v>
+        <v>2026.08.24 00:00</v>
       </c>
       <c r="D9" t="str">
-        <v>2026.08.26 01:00</v>
+        <v>2026.08.24 01:00</v>
       </c>
       <c r="E9" t="str">
-        <v>Teszt Szépségszalon</v>
+        <v>LIDL HU 274 Budapest</v>
       </c>
       <c r="F9">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2215,7 +3615,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J9">
-        <v>149820</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10">
@@ -2226,16 +3626,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C10" t="str">
-        <v>2026.08.31 00:00</v>
+        <v>2026.08.27 00:00</v>
       </c>
       <c r="D10" t="str">
-        <v>2026.08.31 01:00</v>
+        <v>2026.08.27 01:00</v>
       </c>
       <c r="E10" t="str">
-        <v>Példa Notino</v>
+        <v>Bolt</v>
       </c>
       <c r="F10">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2247,7 +3647,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J10">
-        <v>149813</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11">
@@ -2258,16 +3658,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C11" t="str">
-        <v>2026.09.07 00:00</v>
+        <v>2026.09.05 00:00</v>
       </c>
       <c r="D11" t="str">
-        <v>2026.09.07 01:00</v>
+        <v>2026.09.05 01:00</v>
       </c>
       <c r="E11" t="str">
-        <v>Minta Utalás</v>
+        <v>Quentin's Burger Budap</v>
       </c>
       <c r="F11">
-        <v>-31</v>
+        <v>-12</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2279,7 +3679,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J11">
-        <v>149782</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12">
@@ -2290,16 +3690,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C12" t="str">
-        <v>2026.09.13 00:00</v>
+        <v>2026.09.09 00:00</v>
       </c>
       <c r="D12" t="str">
-        <v>2026.09.13 01:00</v>
+        <v>2026.09.09 01:00</v>
       </c>
       <c r="E12" t="str">
-        <v>Minta Pilates</v>
+        <v>Anthropic</v>
       </c>
       <c r="F12">
-        <v>-7</v>
+        <v>-18</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2311,27 +3711,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J12">
-        <v>149775</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Csere</v>
       </c>
       <c r="B13" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C13" t="str">
-        <v>2026.09.20 00:00</v>
+        <v>2026.09.13 00:00</v>
       </c>
       <c r="D13" t="str">
-        <v>2026.09.20 01:00</v>
+        <v>2026.09.13 01:00</v>
       </c>
       <c r="E13" t="str">
-        <v>Teszt Átutalás</v>
+        <v>Devizaváltás HUF pénznemre</v>
       </c>
       <c r="F13">
-        <v>-33</v>
+        <v>-60</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2343,19 +3743,51 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J13">
-        <v>149742</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026.09.15 00:00</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026.09.15 01:00</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Bolt</v>
+      </c>
+      <c r="F14">
+        <v>-26</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I14" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J14">
+        <v>435</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2391,22 +3823,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Feltöltés</v>
       </c>
       <c r="B2" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C2" t="str">
-        <v>2026.08.09 00:00</v>
+        <v>2026.08.08 00:00</v>
       </c>
       <c r="D2" t="str">
-        <v>2026.08.09 01:00</v>
+        <v>2026.08.08 00:00</v>
       </c>
       <c r="E2" t="str">
-        <v>Fikció Műköröm</v>
+        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
       </c>
       <c r="F2">
-        <v>-17164</v>
+        <v>5999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2418,27 +3850,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J2">
-        <v>72836</v>
+        <v>305999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B3" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C3" t="str">
-        <v>2026.08.11 00:00</v>
+        <v>2026.08.10 00:00</v>
       </c>
       <c r="D3" t="str">
-        <v>2026.08.11 01:00</v>
+        <v>2026.08.10 01:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Teszt Átutalás</v>
+        <v>Átutalás neki: Teszt Anna</v>
       </c>
       <c r="F3">
-        <v>-23496</v>
+        <v>-29859</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2450,7 +3882,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J3">
-        <v>49340</v>
+        <v>276140</v>
       </c>
     </row>
     <row r="4">
@@ -2467,10 +3899,10 @@
         <v>2026.08.12 01:00</v>
       </c>
       <c r="E4" t="str">
-        <v>Fikció Tchibo</v>
+        <v>Bolt</v>
       </c>
       <c r="F4">
-        <v>-23392</v>
+        <v>-3892</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2482,27 +3914,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J4">
-        <v>25948</v>
+        <v>272248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B5" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C5" t="str">
-        <v>2026.08.14 00:00</v>
+        <v>2026.08.12 00:00</v>
       </c>
       <c r="D5" t="str">
-        <v>2026.08.14 01:00</v>
+        <v>2026.08.12 01:00</v>
       </c>
       <c r="E5" t="str">
-        <v>Teszt Telekom</v>
+        <v>Átutalás neki: Teszt Anna</v>
       </c>
       <c r="F5">
-        <v>-7394</v>
+        <v>-28221</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2514,30 +3946,30 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J5">
-        <v>18554</v>
+        <v>244027</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Feltöltés</v>
+        <v>Csere</v>
       </c>
       <c r="B6" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C6" t="str">
-        <v>2026.08.15 00:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="D6" t="str">
-        <v>2026.08.15 00:00</v>
+        <v>2026.08.13 01:00</v>
       </c>
       <c r="E6" t="str">
-        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+        <v>Devizaváltás EUR pénznemre</v>
       </c>
       <c r="F6">
-        <v>13278</v>
+        <v>-60000</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H6" t="str">
         <v>HUF</v>
@@ -2546,7 +3978,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J6">
-        <v>31832</v>
+        <v>183727</v>
       </c>
     </row>
     <row r="7">
@@ -2557,16 +3989,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C7" t="str">
-        <v>2026.08.17 00:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="D7" t="str">
-        <v>2026.08.17 01:00</v>
+        <v>2026.08.13 01:00</v>
       </c>
       <c r="E7" t="str">
-        <v>Teszt Apple.com</v>
+        <v>Dentalia Medicina</v>
       </c>
       <c r="F7">
-        <v>-6674</v>
+        <v>-13237</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2578,27 +4010,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J7">
-        <v>25158</v>
+        <v>170490</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Feltöltés</v>
       </c>
       <c r="B8" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C8" t="str">
-        <v>2026.08.20 00:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="D8" t="str">
-        <v>2026.08.20 01:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="E8" t="str">
-        <v>Teszt Persely</v>
+        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
       </c>
       <c r="F8">
-        <v>-38372</v>
+        <v>13278</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2610,7 +4042,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J8">
-        <v>-13214</v>
+        <v>183768</v>
       </c>
     </row>
     <row r="9">
@@ -2621,16 +4053,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C9" t="str">
-        <v>2026.08.22 00:00</v>
+        <v>2026.08.14 00:00</v>
       </c>
       <c r="D9" t="str">
-        <v>2026.08.22 01:00</v>
+        <v>2026.08.14 01:00</v>
       </c>
       <c r="E9" t="str">
-        <v>Fikció Hobby</v>
+        <v>BERSHKA BUDAPEST</v>
       </c>
       <c r="F9">
-        <v>-3058</v>
+        <v>-5278</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2642,7 +4074,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J9">
-        <v>-16272</v>
+        <v>178490</v>
       </c>
     </row>
     <row r="10">
@@ -2653,16 +4085,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C10" t="str">
-        <v>2026.08.23 00:00</v>
+        <v>2026.08.16 00:00</v>
       </c>
       <c r="D10" t="str">
-        <v>2026.08.23 01:00</v>
+        <v>2026.08.16 01:00</v>
       </c>
       <c r="E10" t="str">
-        <v>Teszt Mav</v>
+        <v>COOP MINI ÉLELMISZER</v>
       </c>
       <c r="F10">
-        <v>-10772</v>
+        <v>-7261</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2674,27 +4106,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J10">
-        <v>-27044</v>
+        <v>171229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Feltöltés</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B11" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C11" t="str">
-        <v>2026.08.28 00:00</v>
+        <v>2026.08.17 00:00</v>
       </c>
       <c r="D11" t="str">
-        <v>2026.08.28 00:00</v>
+        <v>2026.08.17 01:00</v>
       </c>
       <c r="E11" t="str">
-        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+        <v>LIDL HU 335 Budapest</v>
       </c>
       <c r="F11">
-        <v>7309</v>
+        <v>-2345</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2706,27 +4138,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J11">
-        <v>-19735</v>
+        <v>168884</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B12" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C12" t="str">
-        <v>2026.09.05 00:00</v>
+        <v>2026.08.17 00:00</v>
       </c>
       <c r="D12" t="str">
-        <v>2026.09.05 01:00</v>
+        <v>2026.08.17 01:00</v>
       </c>
       <c r="E12" t="str">
-        <v>Minta Fodrász</v>
+        <v>Átutalás neki: Teszt Anna</v>
       </c>
       <c r="F12">
-        <v>-11295</v>
+        <v>-21790</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2738,7 +4170,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J12">
-        <v>-31030</v>
+        <v>147094</v>
       </c>
     </row>
     <row r="13">
@@ -2749,16 +4181,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C13" t="str">
-        <v>2026.09.06 00:00</v>
+        <v>2026.08.19 00:00</v>
       </c>
       <c r="D13" t="str">
-        <v>2026.09.06 01:00</v>
+        <v>2026.08.19 01:00</v>
       </c>
       <c r="E13" t="str">
-        <v>Teszt Átutalás</v>
+        <v>Pesti Pilates</v>
       </c>
       <c r="F13">
-        <v>-12907</v>
+        <v>-4163</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2770,27 +4202,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J13">
-        <v>-43937</v>
+        <v>142931</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Feltöltés</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B14" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C14" t="str">
-        <v>2026.09.06 00:00</v>
+        <v>2026.08.21 00:00</v>
       </c>
       <c r="D14" t="str">
-        <v>2026.09.06 00:00</v>
+        <v>2026.08.21 01:00</v>
       </c>
       <c r="E14" t="str">
-        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+        <v>My Green Cup</v>
       </c>
       <c r="F14">
-        <v>7559</v>
+        <v>-5468</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2802,7 +4234,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J14">
-        <v>-36378</v>
+        <v>137463</v>
       </c>
     </row>
     <row r="15">
@@ -2813,16 +4245,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C15" t="str">
-        <v>2026.09.09 00:00</v>
+        <v>2026.08.22 00:00</v>
       </c>
       <c r="D15" t="str">
-        <v>2026.09.09 01:00</v>
+        <v>2026.08.22 01:00</v>
       </c>
       <c r="E15" t="str">
-        <v>Példa Tesco</v>
+        <v>Cafe+Co HU 223562</v>
       </c>
       <c r="F15">
-        <v>-2348</v>
+        <v>-2872</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2834,27 +4266,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J15">
-        <v>-38726</v>
+        <v>134591</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Feltöltés</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B16" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C16" t="str">
-        <v>2026.09.09 00:00</v>
+        <v>2026.08.23 00:00</v>
       </c>
       <c r="D16" t="str">
-        <v>2026.09.09 00:00</v>
+        <v>2026.08.23 01:00</v>
       </c>
       <c r="E16" t="str">
-        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+        <v>COOP MINI ÉLELMISZER</v>
       </c>
       <c r="F16">
-        <v>11146</v>
+        <v>-6066</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2866,7 +4298,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J16">
-        <v>-27580</v>
+        <v>128525</v>
       </c>
     </row>
     <row r="17">
@@ -2877,16 +4309,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C17" t="str">
-        <v>2026.09.10 00:00</v>
+        <v>2026.08.24 00:00</v>
       </c>
       <c r="D17" t="str">
-        <v>2026.09.10 01:00</v>
+        <v>2026.08.24 01:00</v>
       </c>
       <c r="E17" t="str">
-        <v>Fikció Benzinkút</v>
+        <v>SMPLPAY*KNORR-BREMSE 6</v>
       </c>
       <c r="F17">
-        <v>-5265</v>
+        <v>-2206</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2898,7 +4330,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J17">
-        <v>-32845</v>
+        <v>126319</v>
       </c>
     </row>
     <row r="18">
@@ -2909,16 +4341,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C18" t="str">
-        <v>2026.09.11 00:00</v>
+        <v>2026.08.26 00:00</v>
       </c>
       <c r="D18" t="str">
-        <v>2026.09.11 01:00</v>
+        <v>2026.08.26 01:00</v>
       </c>
       <c r="E18" t="str">
-        <v>Teszt Átutalás</v>
+        <v>PIREX PAPÍR ETELE</v>
       </c>
       <c r="F18">
-        <v>-9727</v>
+        <v>-13899</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2930,27 +4362,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J18">
-        <v>-42572</v>
+        <v>112420</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Feltöltés</v>
       </c>
       <c r="B19" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C19" t="str">
-        <v>2026.09.16 00:00</v>
+        <v>2026.08.27 00:00</v>
       </c>
       <c r="D19" t="str">
-        <v>2026.09.16 01:00</v>
+        <v>2026.08.27 00:00</v>
       </c>
       <c r="E19" t="str">
-        <v>Minta Fodrász</v>
+        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
       </c>
       <c r="F19">
-        <v>-6991</v>
+        <v>11955</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2962,7 +4394,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J19">
-        <v>-49563</v>
+        <v>124375</v>
       </c>
     </row>
     <row r="20">
@@ -2973,16 +4405,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C20" t="str">
-        <v>2026.09.21 00:00</v>
+        <v>2026.08.30 00:00</v>
       </c>
       <c r="D20" t="str">
-        <v>2026.09.21 01:00</v>
+        <v>2026.08.30 01:00</v>
       </c>
       <c r="E20" t="str">
-        <v>Teszt Bolt</v>
+        <v>SMPLPAY*KNORR-BREMSE 6</v>
       </c>
       <c r="F20">
-        <v>-3379</v>
+        <v>-2212</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2994,19 +4426,787 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J20">
-        <v>-52942</v>
+        <v>122163</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026.08.31 00:00</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026.08.31 01:00</v>
+      </c>
+      <c r="E21" t="str">
+        <v>DECATHLON NYUGATI TÉR</v>
+      </c>
+      <c r="F21">
+        <v>-23848</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I21" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J21">
+        <v>98315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026.09.01 00:00</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026.09.01 01:00</v>
+      </c>
+      <c r="E22" t="str">
+        <v>ROSSMANN 241.</v>
+      </c>
+      <c r="F22">
+        <v>-6476</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I22" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J22">
+        <v>91839</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026.09.04 00:00</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026.09.04 01:00</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Bolt</v>
+      </c>
+      <c r="F23">
+        <v>-7754</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I23" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J23">
+        <v>84085</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026.09.05 00:00</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026.09.05 01:00</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Pesti Pilates</v>
+      </c>
+      <c r="F24">
+        <v>-13313</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I24" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J24">
+        <v>70772</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026.09.06 00:00</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026.09.06 01:00</v>
+      </c>
+      <c r="E25" t="str">
+        <v>BKK AUTOMATA - I11</v>
+      </c>
+      <c r="F25">
+        <v>-3950</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I25" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J25">
+        <v>66822</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026.09.07 00:00</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026.09.07 01:00</v>
+      </c>
+      <c r="E26" t="str">
+        <v>DM 080 VÁMHÁZ KÖRÚ</v>
+      </c>
+      <c r="F26">
+        <v>-5542</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I26" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J26">
+        <v>61280</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026.09.08 00:00</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026.09.08 01:00</v>
+      </c>
+      <c r="E27" t="str">
+        <v>ROSSMANN 241.</v>
+      </c>
+      <c r="F27">
+        <v>-4600</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I27" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J27">
+        <v>56680</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026.09.09 00:00</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026.09.09 01:00</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Cafe+Co HU 223562</v>
+      </c>
+      <c r="F28">
+        <v>-4879</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I28" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J28">
+        <v>51801</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Feltöltés</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2026.09.09 00:00</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026.09.09 00:00</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+      </c>
+      <c r="F29">
+        <v>5494</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I29" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J29">
+        <v>57295</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2026.09.10 00:00</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026.09.10 01:00</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Cafe+Co HU 223562</v>
+      </c>
+      <c r="F30">
+        <v>-3657</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I30" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J30">
+        <v>53638</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2026.09.11 00:00</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026.09.11 01:00</v>
+      </c>
+      <c r="E31" t="str">
+        <v>BARION *Jegy.hu</v>
+      </c>
+      <c r="F31">
+        <v>-12527</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I31" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J31">
+        <v>41111</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Átutalás</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2026.09.11 00:00</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026.09.11 01:00</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Átutalás neki: Fikció Zsolt</v>
+      </c>
+      <c r="F32">
+        <v>-9589</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I32" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J32">
+        <v>31522</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Feltöltés</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026.09.12 00:00</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026.09.12 00:00</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+      </c>
+      <c r="F33">
+        <v>7039</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I33" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J33">
+        <v>38561</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Csere</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2026.09.13 00:00</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026.09.13 01:00</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Devizaváltás HUF pénznemre</v>
+      </c>
+      <c r="F34">
+        <v>24000</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I34" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J34">
+        <v>62561</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026.09.13 00:00</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026.09.13 01:00</v>
+      </c>
+      <c r="E35" t="str">
+        <v>LIPÓTI PÉKSÉG</v>
+      </c>
+      <c r="F35">
+        <v>-7506</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I35" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J35">
+        <v>55055</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026.09.14 00:00</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026.09.14 01:00</v>
+      </c>
+      <c r="E36" t="str">
+        <v>LIDL HU 274 Budapest</v>
+      </c>
+      <c r="F36">
+        <v>-7445</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I36" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J36">
+        <v>47610</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026.09.15 00:00</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026.09.15 01:00</v>
+      </c>
+      <c r="E37" t="str">
+        <v>SumUp *Teszt Edina E</v>
+      </c>
+      <c r="F37">
+        <v>-2524</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I37" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J37">
+        <v>45086</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Átutalás</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026.09.15 00:00</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026.09.15 01:00</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Átutalás neki: Fikció Zsolt</v>
+      </c>
+      <c r="F38">
+        <v>-12983</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I38" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J38">
+        <v>32103</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Átutalás</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026.09.15 00:00</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026.09.15 01:00</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Átutalás tőle: Példa Kata</v>
+      </c>
+      <c r="F39">
+        <v>7293</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I39" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J39">
+        <v>39396</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C40" t="str">
+        <v>2026.09.16 00:00</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026.09.16 01:00</v>
+      </c>
+      <c r="E40" t="str">
+        <v>SIMPLEP*mav-start</v>
+      </c>
+      <c r="F40">
+        <v>-12516</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I40" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J40">
+        <v>26880</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C41" t="str">
+        <v>2026.09.17 00:00</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026.09.17 01:00</v>
+      </c>
+      <c r="E41" t="str">
+        <v>MCD ALLEE</v>
+      </c>
+      <c r="F41">
+        <v>-4148</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I41" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J41">
+        <v>22732</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Feltöltés</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2026.09.17 00:00</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026.09.17 00:00</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Apple Pay összegű feltöltés a(z) *0117 eszközödön</v>
+      </c>
+      <c r="F42">
+        <v>14305</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I42" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J42">
+        <v>37037</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C43" t="str">
+        <v>2026.09.18 00:00</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026.09.18 01:00</v>
+      </c>
+      <c r="E43" t="str">
+        <v>MCD ALLEE</v>
+      </c>
+      <c r="F43">
+        <v>-4795</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I43" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J43">
+        <v>32242</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Kártyás fizetés</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Folyószámla</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2026.09.19 00:00</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026.09.19 01:00</v>
+      </c>
+      <c r="E44" t="str">
+        <v>BKK AUTOMATA - I11</v>
+      </c>
+      <c r="F44">
+        <v>-5170</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" t="str">
+        <v>HUF</v>
+      </c>
+      <c r="I44" t="str">
+        <v>ELVÉGEZVE</v>
+      </c>
+      <c r="J44">
+        <v>27072</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3057,7 +5257,7 @@
         <v>Átutalás tőle: Teszt Anna</v>
       </c>
       <c r="F2">
-        <v>16067</v>
+        <v>25168</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3069,7 +5269,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J2">
-        <v>56067</v>
+        <v>175168</v>
       </c>
     </row>
     <row r="3">
@@ -3089,7 +5289,7 @@
         <v>Átutalás tőle: Minta Béla</v>
       </c>
       <c r="F3">
-        <v>16067</v>
+        <v>25168</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3101,7 +5301,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J3">
-        <v>72134</v>
+        <v>200336</v>
       </c>
     </row>
     <row r="4">
@@ -3112,16 +5312,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C4" t="str">
-        <v>2026.08.08 00:00</v>
+        <v>2026.08.13 00:00</v>
       </c>
       <c r="D4" t="str">
-        <v>2026.08.08 01:00</v>
+        <v>2026.08.13 01:00</v>
       </c>
       <c r="E4" t="str">
-        <v>Minta Mozi</v>
+        <v>LIDL HU 274 Budapest</v>
       </c>
       <c r="F4">
-        <v>-4333</v>
+        <v>-1879</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3133,7 +5333,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J4">
-        <v>67801</v>
+        <v>198457</v>
       </c>
     </row>
     <row r="5">
@@ -3144,16 +5344,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C5" t="str">
-        <v>2026.08.12 00:00</v>
+        <v>2026.08.14 00:00</v>
       </c>
       <c r="D5" t="str">
-        <v>2026.08.12 01:00</v>
+        <v>2026.08.14 01:00</v>
       </c>
       <c r="E5" t="str">
-        <v>Fikció Dent</v>
+        <v>VISION EXPRESS 523.</v>
       </c>
       <c r="F5">
-        <v>-19117</v>
+        <v>-2399</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3165,27 +5365,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J5">
-        <v>48684</v>
+        <v>196058</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B6" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C6" t="str">
-        <v>2026.08.15 00:00</v>
+        <v>2026.08.17 00:00</v>
       </c>
       <c r="D6" t="str">
-        <v>2026.08.15 01:00</v>
+        <v>2026.08.17 00:00</v>
       </c>
       <c r="E6" t="str">
-        <v>Példa Szórakozás</v>
+        <v>Átutalás tőle: Teszt Anna</v>
       </c>
       <c r="F6">
-        <v>-4965</v>
+        <v>23427</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3197,7 +5397,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J6">
-        <v>43719</v>
+        <v>219485</v>
       </c>
     </row>
     <row r="7">
@@ -3214,10 +5414,10 @@
         <v>2026.08.17 00:00</v>
       </c>
       <c r="E7" t="str">
-        <v>Átutalás tőle: Teszt Anna</v>
+        <v>Átutalás tőle: Minta Béla</v>
       </c>
       <c r="F7">
-        <v>22877</v>
+        <v>23427</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3229,27 +5429,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J7">
-        <v>66596</v>
+        <v>242912</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Átutalás</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B8" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C8" t="str">
-        <v>2026.08.17 00:00</v>
+        <v>2026.08.18 00:00</v>
       </c>
       <c r="D8" t="str">
-        <v>2026.08.17 00:00</v>
+        <v>2026.08.18 01:00</v>
       </c>
       <c r="E8" t="str">
-        <v>Átutalás tőle: Minta Béla</v>
+        <v>MVM NEXT ENERGIAK</v>
       </c>
       <c r="F8">
-        <v>22877</v>
+        <v>-20753</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3261,7 +5461,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J8">
-        <v>89473</v>
+        <v>222159</v>
       </c>
     </row>
     <row r="9">
@@ -3272,16 +5472,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C9" t="str">
-        <v>2026.08.19 00:00</v>
+        <v>2026.08.20 00:00</v>
       </c>
       <c r="D9" t="str">
-        <v>2026.08.19 01:00</v>
+        <v>2026.08.20 01:00</v>
       </c>
       <c r="E9" t="str">
-        <v>Minta Fodrász</v>
+        <v>TelekomSzaml*100200301</v>
       </c>
       <c r="F9">
-        <v>-4227</v>
+        <v>-10788</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3293,27 +5493,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J9">
-        <v>85246</v>
+        <v>211371</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B10" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C10" t="str">
-        <v>2026.08.20 00:00</v>
+        <v>2026.08.26 00:00</v>
       </c>
       <c r="D10" t="str">
-        <v>2026.08.20 01:00</v>
+        <v>2026.08.26 00:00</v>
       </c>
       <c r="E10" t="str">
-        <v>Példa Sumup</v>
+        <v>Átutalás tőle: Teszt Anna</v>
       </c>
       <c r="F10">
-        <v>-7573</v>
+        <v>17339</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3325,27 +5525,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J10">
-        <v>77673</v>
+        <v>228710</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B11" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C11" t="str">
-        <v>2026.08.22 00:00</v>
+        <v>2026.08.26 00:00</v>
       </c>
       <c r="D11" t="str">
-        <v>2026.08.22 01:00</v>
+        <v>2026.08.26 00:00</v>
       </c>
       <c r="E11" t="str">
-        <v>Minta Gyn</v>
+        <v>Átutalás tőle: Minta Béla</v>
       </c>
       <c r="F11">
-        <v>-17519</v>
+        <v>17339</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3357,27 +5557,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J11">
-        <v>60154</v>
+        <v>246049</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Átutalás</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B12" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C12" t="str">
-        <v>2026.08.26 00:00</v>
+        <v>2026.08.28 00:00</v>
       </c>
       <c r="D12" t="str">
-        <v>2026.08.26 00:00</v>
+        <v>2026.08.28 01:00</v>
       </c>
       <c r="E12" t="str">
-        <v>Átutalás tőle: Teszt Anna</v>
+        <v>SPAR MAGYARORSZAG KFT.</v>
       </c>
       <c r="F12">
-        <v>23299</v>
+        <v>-6140</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3389,27 +5589,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J12">
-        <v>83453</v>
+        <v>239909</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Átutalás</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B13" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C13" t="str">
-        <v>2026.08.26 00:00</v>
+        <v>2026.08.29 00:00</v>
       </c>
       <c r="D13" t="str">
-        <v>2026.08.26 00:00</v>
+        <v>2026.08.29 01:00</v>
       </c>
       <c r="E13" t="str">
-        <v>Átutalás tőle: Minta Béla</v>
+        <v>DM 233.SZ.</v>
       </c>
       <c r="F13">
-        <v>23299</v>
+        <v>-5080</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3421,27 +5621,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J13">
-        <v>106752</v>
+        <v>234829</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B14" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C14" t="str">
-        <v>2026.08.26 00:00</v>
+        <v>2026.09.04 00:00</v>
       </c>
       <c r="D14" t="str">
-        <v>2026.08.26 01:00</v>
+        <v>2026.09.04 00:00</v>
       </c>
       <c r="E14" t="str">
-        <v>Példa Budapestgo</v>
+        <v>Átutalás tőle: Teszt Anna</v>
       </c>
       <c r="F14">
-        <v>-3876</v>
+        <v>18443</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3453,27 +5653,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J14">
-        <v>102876</v>
+        <v>253272</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B15" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C15" t="str">
-        <v>2026.08.30 00:00</v>
+        <v>2026.09.04 00:00</v>
       </c>
       <c r="D15" t="str">
-        <v>2026.08.30 01:00</v>
+        <v>2026.09.04 00:00</v>
       </c>
       <c r="E15" t="str">
-        <v>Minta Fodrász</v>
+        <v>Átutalás tőle: Minta Béla</v>
       </c>
       <c r="F15">
-        <v>-5442</v>
+        <v>18443</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3485,7 +5685,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J15">
-        <v>97434</v>
+        <v>271715</v>
       </c>
     </row>
     <row r="16">
@@ -3496,16 +5696,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C16" t="str">
-        <v>2026.08.31 00:00</v>
+        <v>2026.09.05 00:00</v>
       </c>
       <c r="D16" t="str">
-        <v>2026.08.31 01:00</v>
+        <v>2026.09.05 01:00</v>
       </c>
       <c r="E16" t="str">
-        <v>Fikció Jonoyogo</v>
+        <v>PIREX PAPÍR ETELE</v>
       </c>
       <c r="F16">
-        <v>-4513</v>
+        <v>-11265</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3517,7 +5717,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J16">
-        <v>92921</v>
+        <v>260450</v>
       </c>
     </row>
     <row r="17">
@@ -3528,16 +5728,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C17" t="str">
-        <v>2026.09.01 00:00</v>
+        <v>2026.09.06 00:00</v>
       </c>
       <c r="D17" t="str">
-        <v>2026.09.01 01:00</v>
+        <v>2026.09.06 01:00</v>
       </c>
       <c r="E17" t="str">
-        <v>Minta Calzedonia</v>
+        <v>SPAR MAGYARORSZAG KFT.</v>
       </c>
       <c r="F17">
-        <v>-23237</v>
+        <v>-7919</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3549,7 +5749,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J17">
-        <v>69684</v>
+        <v>252531</v>
       </c>
     </row>
     <row r="18">
@@ -3560,16 +5760,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C18" t="str">
-        <v>2026.09.03 00:00</v>
+        <v>2026.09.07 00:00</v>
       </c>
       <c r="D18" t="str">
-        <v>2026.09.03 01:00</v>
+        <v>2026.09.07 01:00</v>
       </c>
       <c r="E18" t="str">
-        <v>Teszt Átutalás</v>
+        <v>BARION *Jegy.hu</v>
       </c>
       <c r="F18">
-        <v>-19565</v>
+        <v>-9758</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3581,27 +5781,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J18">
-        <v>50119</v>
+        <v>242773</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Átutalás</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B19" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C19" t="str">
-        <v>2026.09.04 00:00</v>
+        <v>2026.09.09 00:00</v>
       </c>
       <c r="D19" t="str">
-        <v>2026.09.04 00:00</v>
+        <v>2026.09.09 01:00</v>
       </c>
       <c r="E19" t="str">
-        <v>Átutalás tőle: Teszt Anna</v>
+        <v>Lipoti Pekseg Bartok</v>
       </c>
       <c r="F19">
-        <v>23703</v>
+        <v>-5315</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3613,7 +5813,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J19">
-        <v>73822</v>
+        <v>237458</v>
       </c>
     </row>
     <row r="20">
@@ -3624,16 +5824,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C20" t="str">
-        <v>2026.09.04 00:00</v>
+        <v>2026.09.13 00:00</v>
       </c>
       <c r="D20" t="str">
-        <v>2026.09.04 00:00</v>
+        <v>2026.09.13 00:00</v>
       </c>
       <c r="E20" t="str">
-        <v>Átutalás tőle: Minta Béla</v>
+        <v>Átutalás tőle: Teszt Anna</v>
       </c>
       <c r="F20">
-        <v>23703</v>
+        <v>33657</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3645,27 +5845,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J20">
-        <v>97525</v>
+        <v>271115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Kártyás fizetés</v>
+        <v>Átutalás</v>
       </c>
       <c r="B21" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C21" t="str">
-        <v>2026.09.04 00:00</v>
+        <v>2026.09.13 00:00</v>
       </c>
       <c r="D21" t="str">
-        <v>2026.09.04 01:00</v>
+        <v>2026.09.13 00:00</v>
       </c>
       <c r="E21" t="str">
-        <v>Minta Pizzé</v>
+        <v>Átutalás tőle: Minta Béla</v>
       </c>
       <c r="F21">
-        <v>-5249</v>
+        <v>33657</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3677,7 +5877,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J21">
-        <v>92276</v>
+        <v>304772</v>
       </c>
     </row>
     <row r="22">
@@ -3688,16 +5888,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C22" t="str">
-        <v>2026.09.05 00:00</v>
+        <v>2026.09.13 00:00</v>
       </c>
       <c r="D22" t="str">
-        <v>2026.09.05 01:00</v>
+        <v>2026.09.13 01:00</v>
       </c>
       <c r="E22" t="str">
-        <v>Fikció Klinika</v>
+        <v>LIPÓTI PÉKSÉG</v>
       </c>
       <c r="F22">
-        <v>-7815</v>
+        <v>-7885</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3709,7 +5909,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J22">
-        <v>84461</v>
+        <v>296887</v>
       </c>
     </row>
     <row r="23">
@@ -3720,16 +5920,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C23" t="str">
-        <v>2026.09.09 00:00</v>
+        <v>2026.09.15 00:00</v>
       </c>
       <c r="D23" t="str">
-        <v>2026.09.09 01:00</v>
+        <v>2026.09.15 01:00</v>
       </c>
       <c r="E23" t="str">
-        <v>Minta Garázs</v>
+        <v>Lidl</v>
       </c>
       <c r="F23">
-        <v>-12603</v>
+        <v>-5075</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3741,7 +5941,7 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J23">
-        <v>71858</v>
+        <v>291812</v>
       </c>
     </row>
     <row r="24">
@@ -3752,16 +5952,16 @@
         <v>Folyószámla</v>
       </c>
       <c r="C24" t="str">
-        <v>2026.09.12 00:00</v>
+        <v>2026.09.18 00:00</v>
       </c>
       <c r="D24" t="str">
-        <v>2026.09.12 01:00</v>
+        <v>2026.09.18 01:00</v>
       </c>
       <c r="E24" t="str">
-        <v>Teszt Könyváruház</v>
+        <v>MVM NEXT ENERGIAK</v>
       </c>
       <c r="F24">
-        <v>-14094</v>
+        <v>-26771</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3773,27 +5973,27 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J24">
-        <v>57764</v>
+        <v>265041</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Átutalás</v>
+        <v>Kártyás fizetés</v>
       </c>
       <c r="B25" t="str">
         <v>Folyószámla</v>
       </c>
       <c r="C25" t="str">
-        <v>2026.09.13 00:00</v>
+        <v>2026.09.20 00:00</v>
       </c>
       <c r="D25" t="str">
-        <v>2026.09.13 00:00</v>
+        <v>2026.09.20 01:00</v>
       </c>
       <c r="E25" t="str">
-        <v>Átutalás tőle: Teszt Anna</v>
+        <v>TelekomSzaml*100200301</v>
       </c>
       <c r="F25">
-        <v>37333</v>
+        <v>-9756</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3805,108 +6005,12 @@
         <v>ELVÉGEZVE</v>
       </c>
       <c r="J25">
-        <v>95097</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Átutalás</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Folyószámla</v>
-      </c>
-      <c r="C26" t="str">
-        <v>2026.09.13 00:00</v>
-      </c>
-      <c r="D26" t="str">
-        <v>2026.09.13 00:00</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Átutalás tőle: Minta Béla</v>
-      </c>
-      <c r="F26">
-        <v>37333</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26" t="str">
-        <v>HUF</v>
-      </c>
-      <c r="I26" t="str">
-        <v>ELVÉGEZVE</v>
-      </c>
-      <c r="J26">
-        <v>132430</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Kártyás fizetés</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Folyószámla</v>
-      </c>
-      <c r="C27" t="str">
-        <v>2026.09.13 00:00</v>
-      </c>
-      <c r="D27" t="str">
-        <v>2026.09.13 01:00</v>
-      </c>
-      <c r="E27" t="str">
-        <v>Teszt Pho</v>
-      </c>
-      <c r="F27">
-        <v>-3041</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27" t="str">
-        <v>HUF</v>
-      </c>
-      <c r="I27" t="str">
-        <v>ELVÉGEZVE</v>
-      </c>
-      <c r="J27">
-        <v>129389</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Kártyás fizetés</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Folyószámla</v>
-      </c>
-      <c r="C28" t="str">
-        <v>2026.09.20 00:00</v>
-      </c>
-      <c r="D28" t="str">
-        <v>2026.09.20 01:00</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Minta Fodrász</v>
-      </c>
-      <c r="F28">
-        <v>-4351</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" t="str">
-        <v>HUF</v>
-      </c>
-      <c r="I28" t="str">
-        <v>ELVÉGEZVE</v>
-      </c>
-      <c r="J28">
-        <v>125038</v>
+        <v>255285</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>